--- a/public/fun/pack/xlsx/policy/보험증권정리표_19_부모님용_반딧불마을.xlsx
+++ b/public/fun/pack/xlsx/policy/보험증권정리표_19_부모님용_반딧불마을.xlsx
@@ -31,7 +31,7 @@
     <t>부모님용 보험 증권 정리표</t>
   </si>
   <si>
-    <t>“작은 불빛 같은 기록이 큰 안심이 됩니다”</t>
+    <t>“납입 기간과 만기를 구분해 정리해요”</t>
   </si>
   <si>
     <t>반딧불 마을 테마</t>

--- a/public/fun/pack/xlsx/policy/보험증권정리표_19_부모님용_반딧불마을.xlsx
+++ b/public/fun/pack/xlsx/policy/보험증권정리표_19_부모님용_반딧불마을.xlsx
@@ -26,12 +26,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
   <si>
     <t>부모님용 보험 증권 정리표</t>
-  </si>
-  <si>
-    <t>“납입 기간과 만기를 구분해 정리해요”</t>
   </si>
   <si>
     <t>반딧불 마을 테마</t>
@@ -1401,79 +1398,77 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="2:3" ht="6" customHeight="1"/>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="2:3" ht="22" customHeight="1">
       <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="32" customHeight="1">
       <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="32" customHeight="1">
       <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="22" customHeight="1">
       <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="22" customHeight="1">
       <c r="B11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="28" customHeight="1">
       <c r="B13" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="8"/>
     </row>
     <row r="14" spans="2:3" ht="28" customHeight="1">
       <c r="B14" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="8"/>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="9"/>
     </row>
@@ -1533,9 +1528,7 @@
       <c r="N1" s="10"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1552,22 +1545,22 @@
     </row>
     <row r="3" spans="1:14">
       <c r="B3" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
@@ -1600,46 +1593,46 @@
     </row>
     <row r="5" spans="1:14" ht="28" customHeight="1">
       <c r="A5" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="J5" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="L5" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="N5" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1647,16 +1640,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>68</v>
-      </c>
       <c r="E6" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="18">
         <v>44635</v>
@@ -1665,7 +1658,7 @@
         <v>51940</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I6" s="19">
         <v>52000</v>
@@ -1675,17 +1668,17 @@
         <v>0</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" s="21">
         <f>IF(OR(G6="",K6&lt;&gt;"유지"),"",G6-TODAY())</f>
         <v>0</v>
       </c>
       <c r="M6" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="22" t="s">
         <v>69</v>
-      </c>
-      <c r="N6" s="22" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1693,16 +1686,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>72</v>
-      </c>
       <c r="E7" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="18">
         <v>45108</v>
@@ -1711,7 +1704,7 @@
         <v>46387</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="19">
         <v>18000</v>
@@ -1721,17 +1714,17 @@
         <v>0</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L7" s="21">
         <f>IF(OR(G7="",K7&lt;&gt;"유지"),"",G7-TODAY())</f>
         <v>0</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1739,16 +1732,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="18">
         <v>43789</v>
@@ -1757,7 +1750,7 @@
         <v>54747</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I8" s="19">
         <v>600000</v>
@@ -1767,14 +1760,14 @@
         <v>0</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L8" s="21">
         <f>IF(OR(G8="",K8&lt;&gt;"유지"),"",G8-TODAY())</f>
         <v>0</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N8" s="22"/>
     </row>
@@ -2980,7 +2973,7 @@
   <sheetData>
     <row r="1" spans="2:10">
       <c r="B1" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C1" s="23"/>
       <c r="D1" s="23"/>
@@ -2993,28 +2986,28 @@
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>78</v>
-      </c>
       <c r="G3" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>77</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -3223,7 +3216,7 @@
     </row>
     <row r="10" spans="2:10">
       <c r="B10" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="28">
         <f>SUM(C4:C9)</f>
@@ -3271,10 +3264,10 @@
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G12" s="24">
         <f>'설정'!C12</f>
@@ -3295,7 +3288,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" s="25">
         <f>COUNTIFS('정리표'!$L$6:$L$55,"&gt;=0",'정리표'!$L$6:$L$55,"&lt;=30")</f>
@@ -3320,7 +3313,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="B14" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" s="25">
         <f>COUNTIFS('정리표'!$L$6:$L$55,"&gt;=0",'정리표'!$L$6:$L$55,"&lt;=90")</f>
@@ -3345,7 +3338,7 @@
     </row>
     <row r="15" spans="2:10">
       <c r="B15" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="25">
         <f>COUNTIFS('정리표'!$L$6:$L$55,"&gt;=0",'정리표'!$L$6:$L$55,"&lt;=180")</f>
@@ -3370,7 +3363,7 @@
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="25">
         <f>COUNTIFS('정리표'!$L$6:$L$55,"&gt;=0",'정리표'!$L$6:$L$55,"&lt;=365")</f>
@@ -3395,14 +3388,14 @@
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" s="25">
         <f>COUNTIFS('정리표'!$L$6:$L$55,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H17" s="28">
         <f>SUM(H4:H16)</f>
@@ -3440,7 +3433,7 @@
   <sheetData>
     <row r="1" spans="2:8">
       <c r="B1" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C1" s="23"/>
       <c r="D1" s="23"/>
@@ -3451,7 +3444,7 @@
     </row>
     <row r="2" spans="2:8">
       <c r="B2" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" s="18">
         <v>46023</v>
@@ -3459,7 +3452,7 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" s="14">
         <f>'설정'!B4</f>
@@ -3488,7 +3481,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -3499,7 +3492,7 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3510,7 +3503,7 @@
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -3521,7 +3514,7 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
@@ -3532,7 +3525,7 @@
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -3543,7 +3536,7 @@
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -3554,7 +3547,7 @@
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -3565,7 +3558,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -3576,7 +3569,7 @@
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -3587,7 +3580,7 @@
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
@@ -3598,7 +3591,7 @@
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -3609,7 +3602,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
@@ -3620,7 +3613,7 @@
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
@@ -3631,7 +3624,7 @@
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -3689,7 +3682,7 @@
   <sheetData>
     <row r="1" spans="2:7">
       <c r="B1" s="23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1" s="23"/>
       <c r="D1" s="23"/>
@@ -3699,132 +3692,132 @@
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:7">
       <c r="C11" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="C12" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="2:7">
       <c r="C13" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="2:7">
       <c r="C14" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="C15" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="C16" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/public/fun/pack/xlsx/policy/보험증권정리표_19_부모님용_반딧불마을.xlsx
+++ b/public/fun/pack/xlsx/policy/보험증권정리표_19_부모님용_반딧불마을.xlsx
@@ -73,7 +73,7 @@
     <t>주민등록번호·계좌번호 같은 민감한 정보는 적지 않는 것을 권해요. 증권 번호 대신 ‘보관 위치’를 적어 두세요.</t>
   </si>
   <si>
-    <t>우체국보험 상담 안내 · 자유롭게 고쳐 쓰세요</t>
+    <t>반딧불이의 곳간 · 자유롭게 고쳐 쓰세요</t>
   </si>
   <si>
     <t>설정 — 이름을 우리 집에 맞게 바꿔요</t>
@@ -226,7 +226,7 @@
     <t>보관 위치</t>
   </si>
   <si>
-    <t>우체국</t>
+    <t>보험사</t>
   </si>
   <si>
     <t>예시 상품(지우고 쓰세요)</t>
@@ -328,7 +328,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="m&quot;월&quot; d&quot;일&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot;일 남음&quot;;&quot;기간 지남&quot;"/>
     <numFmt numFmtId="167" formatCode="0%"/>
   </numFmts>
